--- a/EBS명의_2024-2026.xlsx
+++ b/EBS명의_2024-2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21345" windowHeight="9120"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21165" windowHeight="6690"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="EBS명의" sheetId="1" r:id="rId4"/>
@@ -22,7 +22,772 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="395">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="448">
+  <x:si>
+    <x:t>https://www.amc.seoul.kr/asan/main.do; https://ch.cauhs.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.amc.seoul.kr/asan/main.do; https://www.khnmc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.snuh.org/; https://www.amc.seoul.kr/asan/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.bohun.or.kr/seoul/main.do; https://seoul.hyumc.com/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.khnmc.or.kr/; https://www.amc.seoul.kr/asan/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.gilhospital.com/; https://www.schmc.ac.kr/seoul/index.do; https://snubh.org/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.masan.samsung.com/; https://seoul.eumc.ac.kr/; https://www.cmcseoul.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.snuh.org/; https://www.eulji.or.kr/; https://med.khmc.or.kr/kr/main.do; https://www.amc.seoul.kr/asan/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.khnmc.or.kr/; https://gs.severance.healthcare/gs/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://hosp.ajoumc.or.kr/; https://ch.cauhs.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방영일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오수영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이진구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원태빈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김장용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신성재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이성진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임태강</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주은연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김문규</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김이수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송채린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이주엽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배지훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정연훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손일석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박정환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정선근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강석호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장석준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이정일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정지향</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김병준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주원일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김광균</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김현승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김동준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김범준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임선교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김도영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임홍의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김영훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김치경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>—</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피부과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임현국</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박광열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박준성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정희원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문지연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김훈수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김건하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김현아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고홍섭</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구교철</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정은재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김치헌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한승환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김병극</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백남종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>변재용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박중현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박종재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전영수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윤진숙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박찬기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이지영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이은정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강진모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방오영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한웅규</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박관규</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박민선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김용배</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이순태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오성진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최용범</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천동일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김범택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상협</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이두익</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김도헌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이창영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박성미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김명서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최성혜</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최기원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박기혁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김세혁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강경중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이재성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안영근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오승준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임기정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오병호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김성환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하태경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신유섭</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김지훈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신승윤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우상욱</x:t>
+  </x:si>
+  <x:si>
+    <x:t>치주과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진동규</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김미란</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배하석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서재현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임승재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윤원기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이양원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폐결절</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이유진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김재현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요로결석 (내 몸의 걸림돌)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강동경희대 / 서울아산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>순환기내과 / 소화기내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>순환기내과 / 심장외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울성모병원 / 성빈센트병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌전증 (난치에서 완치로)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>순환기내과 / 흉부외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정의학과 / 내분비내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분당서울대 / 강동경희대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어환 · 윤하나 · 채정호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두통 (국민 질환, 두통)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>순환기내과 / 심장내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대장항문외과 / 소화기내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복막암 (포기하기엔 이르다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정형외과 / 마취통증의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박경민 · 박승정 · 조양현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유방암 (젊어서 무서운)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방광암 (혈뇨를 봤다면)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소화기내과 / 위장관외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내분비대사내과 / 소화기외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중앙보훈병원 / 한양대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마취통증의학과 / 정형외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강동경희대 / 강남세브란스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아주대병원 / 중앙대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>녹내장 (실명을 막아라!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비뇨의학과 / 방사선종양학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈장 (장기가 탈출했다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인슐린 펌프, 인공췌장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직장암 (항문으로 가는 길)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간담췌외과 / 소화기내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울아산 / 강동경희대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유방암 (급증하는 유방암)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소화기내과 / 대장항문외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노인 고관절 골절 수술</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경과 / 정신건강의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경추척수증 (목 중풍)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://snubh.org/index.do; https://www.khnmc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안면 질환 (얼굴 통증과 떨림)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대장항문 양성질환 (치질과 변실금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈모 (탈모, 심는 게 답일까?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삼성창원 / 이대서울 / 서울성모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어지럼증 (핑핑 도는 어지럼증)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무릎 관절염 (반월상 연골판)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리통증 (허리를 곧추세우다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위암 (위암과 헤어지는 중입니다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌졸중 인터벤션 (뉴로인터벤션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간암 (첨단의학으로 치료한다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우울증 (지금, 우울하신가요?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임플란트 (임플란트 주위염의 공포)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신장투석 혈관로 (투석혈관로)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적정 체중 (100세 건강 1부)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뼈 건강 (100세 건강 2부)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고위험산모 (태어나줘서 고마워)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코질환 (코에도 종양이 생긴다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공복 혈당 (100세 건강 5부)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난청 (보청기에서 인공와우까지!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어깨 질환 (지긋지긋한 어깨 통증)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심근병증 (심장도 근육이 아프다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인지 노쇠 (100세 건강 4부)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛 중독 (벗어날 수 없는 식탐)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심방세동 (뇌혈관을 공격하다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>췌장암 (장기생존으 가는 길!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최적 혈압 (100세 건강 6부)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폐 이식 (또다시 숨을 쉰다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구강암 (입속 암의 위험 신호)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어깨 재활 (어깨 펴고 삽시다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈성형 (안검하수와 안 성형)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담도·담낭 (돌, 암이 될까요?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알레르기 비염 (면역으로 잡는다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근감소증 (골든타임을 잡아라!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소화기내과 / 심장혈관흉부외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심실부정맥 (파르르 떠는 심장)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신장암 (당신은 눈치챘나요?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심뇌혈관센터 (골든타임을 사수하라)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퇴행성 관절염 (수술이 무서워요)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경동맥 (뇌와 심장의 통로 경동맥)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통풍 (통풍, 당신을 노린다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침샘암 (귀밑의 멍울이 침샘암?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌경색 (뇌경색 응급의 갈림길)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자가면역 뇌염 (뇌염이 찾아왔다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비만 (이것이 망하는 다이어트다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌종양 (몸에서 전이된 뇌암)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오십견 (절대 주사로 낫지 않는다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>척추·척수종양 (걸어서 집으로)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발질환 (아이고 내 발이야!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>치주질환 (잇몸병 2천만 시대)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피부암 (점 빼러 갔다 암선고?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손 질환 (손목이 무너지면…)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어지럼증 (반복되는 어지럼증)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡기내과 / 심장혈관흉부외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정신건강의학과 (수면의학센터장)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심방세동 (뇌졸중 부르는 심방세동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노인 변비 (참으면 독이 된다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.snuh.org/; https://anam.kumc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://sev.severance.healthcare/sev/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.amc.seoul.kr/asan/main.do; https://hosp.ajoumc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cmcseoul.or.kr/; https://www.cmcvincent.or.kr/page/main</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://gs.severance.healthcare/gs/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갱년기 여성 호르몬 치료 (갱년기 호르몬제, 먹을까?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://hangang.hallym.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.inha.com/page/main</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고령 허리질환 (허리 수술, 아프기 전에 미리할까?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cnuh.com/main.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://dongtan.hallym.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.amc.seoul.kr/asan/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>http://ansan.kumc.or.kr/main/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.schmc.ac.kr/seoul/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.bohun.or.kr/seoul/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://med.khmc.or.kr/kr/main.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고지혈증·대사이상증후군 (고지혈증 약, 꼭 먹어야 하나요?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>척추수술 후 실패증후군 (수술받은 허리, 여전히 아픈 이유는?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.samsunghospital.com/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://guro.kumc.or.kr/kr/index.do</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.daehang.com/main/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cmcsungmo.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.gilhospital.com/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://hallym.hallym.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피부 노화 (우리 몸 가장 큰 장기, 피부를 보호하라)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가톨릭대 은평성모병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김진수 · 김형진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울아산 / 중앙대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보영 · 유희태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정기욱 · 최창환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윤정한 · 신혜원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여창동 · 문영규</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이두석 · 김도선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김철민 · 김세홍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임수 · 최성일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한주용 · 손희정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>면역 3부 — 피부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차재명 · 천재영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>면역 2부 — 장</x:t>
+  </x:si>
   <x:si>
     <x:t>황호경 · 방승민</x:t>
   </x:si>
@@ -30,630 +795,87 @@
     <x:t>문호식 · 이준석</x:t>
   </x:si>
   <x:si>
-    <x:t>유방암 (젊어서 무서운)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대장항문외과 / 소화기내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내분비대사내과 / 소화기외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정형외과 / 마취통증의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소화기내과 / 위장관외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>순환기내과 / 심장내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방광암 (혈뇨를 봤다면)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정의학과 / 내분비내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분당서울대 / 강동경희대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>순환기내과 / 심장외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강동경희대 / 서울아산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주대병원 / 중앙대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신경과 / 정신건강의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어환 · 윤하나 · 채정호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인슐린 펌프, 인공췌장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두통 (국민 질환, 두통)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울성모병원 / 성빈센트병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌전증 (난치에서 완치로)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간담췌외과 / 소화기내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중앙보훈병원 / 한양대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유방암 (급증하는 유방암)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복막암 (포기하기엔 이르다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소화기내과 / 대장항문외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노인 고관절 골절 수술</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강동경희대 / 강남세브란스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박경민 · 박승정 · 조양현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요로결석 (내 몸의 걸림돌)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>순환기내과 / 흉부외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>순환기내과 / 소화기내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마취통증의학과 / 정형외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>녹내장 (실명을 막아라!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경추척수증 (목 중풍)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직장암 (항문으로 가는 길)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울아산 / 강동경희대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비뇨의학과 / 방사선종양학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탈장 (장기가 탈출했다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방영일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오수영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이진구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원태빈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김장용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송채린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정연훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배지훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이성진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주원일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신성재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이정일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신경과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박정환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김문규</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임태강</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주은연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김동준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김이수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이주엽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강석호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김광균</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피부과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김병준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임현국</x:t>
-  </x:si>
-  <x:si>
-    <x:t>손일석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장석준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김현승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임홍의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정지향</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정선근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임선교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김치경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김범준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박준성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전영수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김영훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박광열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문지연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김훈수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김병극</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김도영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>변재용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김건하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정희원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>—</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박종재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김치헌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김현아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오성진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고홍섭</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이은정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백남종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구교철</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정은재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최용범</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한승환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박중현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한웅규</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윤진숙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강진모</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박기혁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박찬기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이순태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방오영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박관규</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김용배</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강경중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천동일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이창영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박성미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박민선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이지영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이두익</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안영근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신유섭</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김범택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최성혜</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우상욱</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한문구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김명서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상협</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김도헌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최기원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진동규</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김성환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신승윤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>치주과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김세혁</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배하석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김미란</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김지훈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이재성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이양원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임기정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하태경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이유진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서재현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임승재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윤원기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오병호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오승준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폐결절</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김재현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고지혈증·대사이상증후군 (고지혈증 약, 꼭 먹어야 하나요?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>척추수술 후 실패증후군 (수술받은 허리, 여전히 아픈 이유는?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>난청 (보청기에서 인공와우까지!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위암 (위암과 헤어지는 중입니다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안면 질환 (얼굴 통증과 떨림)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공복 혈당 (100세 건강 5부)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간암 (첨단의학으로 치료한다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대장항문 양성질환 (치질과 변실금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어지럼증 (핑핑 도는 어지럼증)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고위험산모 (태어나줘서 고마워)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무릎 관절염 (반월상 연골판)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우울증 (지금, 우울하신가요?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심근병증 (심장도 근육이 아프다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탈모 (탈모, 심는 게 답일까?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임플란트 (임플란트 주위염의 공포)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌졸중 인터벤션 (뉴로인터벤션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코질환 (코에도 종양이 생긴다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폐 이식 (또다시 숨을 쉰다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적정 체중 (100세 건강 1부)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뼈 건강 (100세 건강 2부)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최적 혈압 (100세 건강 6부)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛 중독 (벗어날 수 없는 식탐)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심방세동 (뇌혈관을 공격하다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>췌장암 (장기생존으 가는 길!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삼성창원 / 이대서울 / 서울성모</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리통증 (허리를 곧추세우다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어깨 질환 (지긋지긋한 어깨 통증)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신장투석 혈관로 (투석혈관로)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인지 노쇠 (100세 건강 4부)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>척추·척수종양 (걸어서 집으로)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어깨 재활 (어깨 펴고 삽시다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심실부정맥 (파르르 떠는 심장)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통풍 (통풍, 당신을 노린다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담도·담낭 (돌, 암이 될까요?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈성형 (안검하수와 안 성형)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심뇌혈관센터 (골든타임을 사수하라)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신장암 (당신은 눈치챘나요?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퇴행성 관절염 (수술이 무서워요)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경동맥 (뇌와 심장의 통로 경동맥)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침샘암 (귀밑의 멍울이 침샘암?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자가면역 뇌염 (뇌염이 찾아왔다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구강암 (입속 암의 위험 신호)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비만 (이것이 망하는 다이어트다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노인 변비 (참으면 독이 된다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정신건강의학과 (수면의학센터장)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근감소증 (골든타임을 잡아라!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소화기내과 / 심장혈관흉부외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌경색 (뇌경색 응급의 갈림길)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>치주질환 (잇몸병 2천만 시대)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발질환 (아이고 내 발이야!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알레르기 비염 (면역으로 잡는다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡기내과 / 심장혈관흉부외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌종양 (몸에서 전이된 뇌암)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오십견 (절대 주사로 낫지 않는다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피부암 (점 빼러 갔다 암선고?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>손 질환 (손목이 무너지면…)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심방세동 (뇌졸중 부르는 심방세동)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어지럼증 (반복되는 어지럼증)</x:t>
+    <x:t>김완욱 · 주지현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임재준 · 심태선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울대 / 서울아산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>면역 1부 — 폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강민주 · 노성원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복부대동맥 질환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대구가톨릭대학교병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혈관중재·혈관외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울대 / 고려대안암</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경과 / 신경외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김한준 · 장진우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최승호 · 이영찬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최영득 · 금웅섭</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생체 장기이식 30년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한림대 한강성심병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경과 (뇌신경센터)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대학교치과병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임재영 · 유승돈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한림대 동탄성심병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김도훈 · 김용희</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가톨릭대 서울성모병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무릎질환 (인공관절 없이 내 무릎을 재건한다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>급성심근경색 (당신의 심장이 멈출 수도 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돌발성 난청 (난청이 있으면 치매가 잘 온다?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자궁 질환 (갱년기 이후, 내 자궁은 안전한가?)</x:t>
   </x:si>
   <x:si>
     <x:t>신촌세브란스병원</x:t>
   </x:si>
   <x:si>
+    <x:t>병원 홈페이지 링크</x:t>
+  </x:si>
+  <x:si>
     <x:t>박원명 · 우영섭</x:t>
   </x:si>
   <x:si>
@@ -663,550 +885,487 @@
     <x:t>이상철 · 김욱성</x:t>
   </x:si>
   <x:si>
+    <x:t>김용찬 · 신진우</x:t>
+  </x:si>
+  <x:si>
     <x:t>서울아산 / 아주대</x:t>
   </x:si>
   <x:si>
     <x:t>정훈용 · 허훈</x:t>
   </x:si>
   <x:si>
-    <x:t>김용찬 · 신진우</x:t>
+    <x:t>국민건강보험 일산병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>치주과 / 보철과</x:t>
   </x:si>
   <x:si>
     <x:t>김영택 · 윤준호</x:t>
   </x:si>
   <x:si>
-    <x:t>국민건강보험 일산병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>치주과 / 보철과</x:t>
+    <x:t>순천향대 서울병원</x:t>
   </x:si>
   <x:si>
     <x:t>강남세브란스병원</x:t>
   </x:si>
   <x:si>
-    <x:t>순천향대 서울병원</x:t>
-  </x:si>
-  <x:si>
     <x:t>김선미 · 류혜진</x:t>
   </x:si>
   <x:si>
-    <x:t>임수 · 최성일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한주용 · 손희정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이두석 · 김도선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김철민 · 김세홍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피부 노화 (우리 몸 가장 큰 장기, 피부를 보호하라)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갱년기 여성 호르몬 치료 (갱년기 호르몬제, 먹을까?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고령 허리질환 (허리 수술, 아프기 전에 미리할까?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자궁 질환 (갱년기 이후, 내 자궁은 안전한가?)</x:t>
+    <x:t>https://www.cmcseoul.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://hosp.ajoumc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>망막 질환 (실명할 수 있습니다 - 망막박리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://knuh.kr/index.asp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cmcep.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.eulji.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울대 / 노원을지대 / 경희대 / 서울아산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.nhimc.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://seoul.hyumc.com/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://anam.kumc.or.kr/</x:t>
   </x:si>
   <x:si>
     <x:t>갑상선 질환 (뇌와 심장을 지키려면 갑상선을)</x:t>
   </x:si>
   <x:si>
+    <x:t>https://seoul.eumc.ac.kr/</x:t>
+  </x:si>
+  <x:si>
     <x:t>백내장·노안수술 (급증하는 젊은 백내장 수술)</x:t>
   </x:si>
   <x:si>
+    <x:t>https://www.khnmc.or.kr/</x:t>
+  </x:si>
+  <x:si>
     <x:t>가슴통증 (가슴통증, 진짜 위험한 이유는?)</x:t>
   </x:si>
   <x:si>
+    <x:t>가정형 호스피스 (삶의 마지막을 치료하다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저속노화 특집 3부 (80대에 중년의 뇌를)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저속노화 특집 2부 (인간은 세 번 늙는다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://mokdong.eumc.ac.kr/</x:t>
+  </x:si>
+  <x:si>
     <x:t>저속노화 특집 1부 (젊게 살려면 명의처럼)</x:t>
   </x:si>
   <x:si>
-    <x:t>저속노화 특집 2부 (인간은 세 번 늙는다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정형 호스피스 (삶의 마지막을 치료하다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저속노화 특집 3부 (80대에 중년의 뇌를)</x:t>
-  </x:si>
-  <x:si>
     <x:t>턱관절 질환 (당신의 턱이 무너지고 있다!)</x:t>
   </x:si>
   <x:si>
+    <x:t>https://snubh.org/index.do</x:t>
+  </x:si>
+  <x:si>
     <x:t>알코올성 치매 (당신이 술을 끊어야 하는 이유)</x:t>
   </x:si>
   <x:si>
+    <x:t>https://main.kbsmc.co.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다리혈관질환 (내 다리가 아픈 진짜 이유는?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폐암 (암 사망률 1위, 폐암이 달라졌어요)</x:t>
+  </x:si>
+  <x:si>
     <x:t>안구종양 (눈 속의 점, 자라면 암이 된다)</x:t>
   </x:si>
   <x:si>
-    <x:t>폐암 (암 사망률 1위, 폐암이 달라졌어요)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다리혈관질환 (내 다리가 아픈 진짜 이유는?)</x:t>
+    <x:t>치매 (알츠하이머! 이제는 치료할 수 있다)</x:t>
   </x:si>
   <x:si>
     <x:t>백령병원 특집 (죽을 때까지 섬을 지키겠습니다)</x:t>
   </x:si>
   <x:si>
-    <x:t>치매 (알츠하이머! 이제는 치료할 수 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>급성심근경색 (당신의 심장이 멈출 수도 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무릎질환 (인공관절 없이 내 무릎을 재건한다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돌발성 난청 (난청이 있으면 치매가 잘 온다?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>망막 질환 (실명할 수 있습니다 - 망막박리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울대 / 노원을지대 / 경희대 / 서울아산</x:t>
+    <x:t>소속병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삼성서울병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산부인과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉부외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>명의이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재활의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경추·목디스크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여의도성모병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경북대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울성모병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이비인후과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울아산병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비뇨의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내분비대사내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강동경희대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정신건강의학과</x:t>
   </x:si>
   <x:si>
     <x:t>혈관외과</x:t>
   </x:si>
   <x:si>
-    <x:t>명의이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흉부외과</x:t>
-  </x:si>
-  <x:si>
     <x:t>정형외과</x:t>
   </x:si>
   <x:si>
-    <x:t>삼성서울병원</x:t>
+    <x:t>고대안암병원</x:t>
   </x:si>
   <x:si>
     <x:t>고려대구로병원</x:t>
   </x:si>
   <x:si>
+    <x:t>중앙대광명병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은평성모병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가천대길병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고대구로병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영상의학과</x:t>
+  </x:si>
+  <x:si>
     <x:t>소화기내과</x:t>
   </x:si>
   <x:si>
-    <x:t>서울아산병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산부인과</x:t>
-  </x:si>
-  <x:si>
     <x:t>모발이식센터</x:t>
   </x:si>
   <x:si>
-    <x:t>은평성모병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여의도성모병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경북대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소속병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정신건강의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비뇨의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중앙대광명병원</x:t>
+    <x:t>심장혈관내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한양대학교병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아주대학교병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건양대학교병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이대서울병원</x:t>
   </x:si>
   <x:si>
     <x:t>노원을지대병원</x:t>
   </x:si>
   <x:si>
-    <x:t>신경외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울성모병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이비인후과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이대서울병원</x:t>
+    <x:t>아주대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장기이식센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화상외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노년내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡기내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인하대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간담췌외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심장내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서울대치과병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세브란스병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건국대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대장항문외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구강내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중앙대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건국대학교병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>족부정형외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강북삼성병원</x:t>
   </x:si>
   <x:si>
     <x:t>중앙대학교병원</x:t>
   </x:si>
   <x:si>
-    <x:t>경추·목디스크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영상의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내분비대사내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고대구로병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재활의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가천대길병원</x:t>
+    <x:t>한림대성심병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비뇨기과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백령병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마취통증의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부산대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이대목동병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>류마티스내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고대안산병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분당서울대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내분비내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전남대병원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>순환기내과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정의학과</x:t>
   </x:si>
   <x:si>
     <x:t>대항병원</x:t>
   </x:si>
   <x:si>
-    <x:t>강동경희대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부산대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노년내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마취통증의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심장혈관내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이대목동병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심장내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한림대성심병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>순환기내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한양대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중앙대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건양대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간담췌외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세브란스병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>류마티스내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구강내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울대치과병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비뇨기과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고대안암병원</x:t>
+    <x:t>고려대안암병원</x:t>
   </x:si>
   <x:si>
     <x:t>알레르기내과</x:t>
   </x:si>
   <x:si>
-    <x:t>건국대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화상외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강북삼성병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>족부정형외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건국대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장기이식센터</x:t>
+    <x:t>유방내분비외과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌동맥류</x:t>
   </x:si>
   <x:si>
     <x:t>두피 질환</x:t>
   </x:si>
   <x:si>
-    <x:t>대장항문외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡기내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내분비내과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분당서울대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌동맥류</x:t>
-  </x:si>
-  <x:si>
     <x:t>파킨슨 증후군</x:t>
   </x:si>
   <x:si>
-    <x:t>고대안산병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유방내분비외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인하대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고려대안암병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백령병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전남대병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김완욱 · 주지현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>면역 1부 — 폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임재준 · 심태선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울대 / 서울아산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차재명 · 천재영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>면역 3부 — 피부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>면역 2부 — 장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강민주 · 노성원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복부대동맥 질환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대구가톨릭대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울대 / 고려대안암</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신경과 / 신경외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김한준 · 장진우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혈관중재·혈관외과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최승호 · 이영찬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최영득 · 금웅섭</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생체 장기이식 30년</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한림대 한강성심병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신경과 (뇌신경센터)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대학교치과병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임재영 · 유승돈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한림대 동탄성심병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김도훈 · 김용희</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가톨릭대 서울성모병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가톨릭대 은평성모병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보영 · 유희태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김진수 · 김형진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정기욱 · 최창환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서울아산 / 중앙대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여창동 · 문영규</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윤정한 · 신혜원</x:t>
-  </x:si>
-  <x:si>
     <x:t>가천대길병원 / 순천향대 / 분당서울대</x:t>
   </x:si>
   <x:si>
+    <x:t>김효수 · 최재웅 · 김원 · 박덕우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신장암 (당신도 모르게 생긴 신장암)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백정흠 · 이태희 · 이동호 · 김나영</x:t>
+  </x:si>
+  <x:si>
     <x:t>심근경색 (막힌 심장 혈관을 뚫어라!)</x:t>
   </x:si>
   <x:si>
+    <x:t>변비와 대장암 (꽉 막힌 대장을 치료하라)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수면장애 (당신은 잘못 자고 있습니다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손·손목질환 (물병도 못 여는 당신에게)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://ch.cauhs.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지방간 (간의 운명, 지방간이 결정한다!)</x:t>
+  </x:si>
+  <x:si>
     <x:t>혈전증 (나도 모르게 혈관이 막힌다면?)</x:t>
   </x:si>
   <x:si>
-    <x:t>수면장애 (당신은 잘못 자고 있습니다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>손·손목질환 (물병도 못 여는 당신에게)</x:t>
-  </x:si>
-  <x:si>
     <x:t>적정 콜레스테롤 (100세 건강 3부)</x:t>
   </x:si>
   <x:si>
-    <x:t>지방간 (간의 운명, 지방간이 결정한다!)</x:t>
+    <x:t>노인우울증 (방치하면 뇌가 망가진다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.snuh.org/</x:t>
   </x:si>
   <x:si>
     <x:t>미니 뇌졸중 (미니 뇌졸중을 아십니까?)</x:t>
   </x:si>
   <x:si>
+    <x:t>피부암 (노인의 피부, 암이 파고든다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신경외과 / 비뇨의학과 / 정신건강의학과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.kyuh.ac.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>염증성 위장질환 (잘 먹고, 잘 싸는 법)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위염 (위염에서 해방되고 싶은 당신에게)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대상포진 (대상포진 통증과 작별하는 법)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.pnuh.or.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다혈관질환 (심혈관이 걱정되는 당신)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식도암 (조용히 스며들어 빠르게 퍼진다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지방사통 (원인 불명 하지 방사통)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식후혈당 (오르락내리락, 당신의 혈당)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당뇨발 (당뇨병 5명 중 1명은 발병)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식도 질환 (음식이 삼켜지지 않는다?!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화상 (화상, 나도 겪을 수 있습니다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.dcmc.co.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전립선암 (피 한 방울에 답이 있다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.snudh.org/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌사자 장기이식 (삶의 기적을 노래하라)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>류마티스 (관절염이 전신을 공격한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.kuh.ac.kr/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>췌장염 (췌장 질환, 작은 불씨가…)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌졸중 재활 (고장난 뇌를 되살린다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발·발목 (무리한 운동! 발목 잡는다!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복부 비만 (안 먹는데 왜 안 빠질까?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌동맥류 (당신의 뇌, 정말 안전한가요?)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파킨슨 (희망을 향한 끝없는 도전!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혈압 (돌연사를 막으려면 적정 혈압을)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공식 홈페이지 주소를 확인하지 못했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안면 신경 마비 (구안와사와 안면마비)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노화와 수면 장애 (치매를 부르는 잠)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대장 용종 (대장에 숨겨진 두번째 위험)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>림프 부종 (몸속 하수구가 막혔다!)</x:t>
+  </x:si>
+  <x:si>
     <x:t>고관절 (당신이 꼭 알아야 할 고관절…)</x:t>
   </x:si>
   <x:si>
-    <x:t>신장암 (당신도 모르게 생긴 신장암)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>염증성 위장질환 (잘 먹고, 잘 싸는 법)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위염 (위염에서 해방되고 싶은 당신에게)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다혈관질환 (심혈관이 걱정되는 당신)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>변비와 대장암 (꽉 막힌 대장을 치료하라)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김효수 · 최재웅 · 김원 · 박덕우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백정흠 · 이태희 · 이동호 · 김나영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노인우울증 (방치하면 뇌가 망가진다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대상포진 (대상포진 통증과 작별하는 법)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식도암 (조용히 스며들어 빠르게 퍼진다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피부암 (노인의 피부, 암이 파고든다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지방사통 (원인 불명 하지 방사통)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발·발목 (무리한 운동! 발목 잡는다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>류마티스 (관절염이 전신을 공격한다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신경외과 / 비뇨의학과 / 정신건강의학과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당뇨발 (당뇨병 5명 중 1명은 발병)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혈압 (돌연사를 막으려면 적정 혈압을)</x:t>
-  </x:si>
-  <x:si>
     <x:t>지방간염 (간이 보내는 마지막 SOS)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식도 질환 (음식이 삼켜지지 않는다?!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노화와 수면 장애 (치매를 부르는 잠)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복부 비만 (안 먹는데 왜 안 빠질까?)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식후혈당 (오르락내리락, 당신의 혈당)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파킨슨 (희망을 향한 끝없는 도전!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안면 신경 마비 (구안와사와 안면마비)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전립선암 (피 한 방울에 답이 있다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화상 (화상, 나도 겪을 수 있습니다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대장 용종 (대장에 숨겨진 두번째 위험)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>림프 부종 (몸속 하수구가 막혔다!)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌사자 장기이식 (삶의 기적을 노래하라)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌졸중 재활 (고장난 뇌를 되살린다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>췌장염 (췌장 질환, 작은 불씨가…)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌동맥류 (당신의 뇌, 정말 안전한가요?)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1268,7 +1427,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border>
       <x:left>
         <x:color indexed="64"/>
@@ -1297,17 +1456,31 @@
         <x:color indexed="64"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color indexed="64"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color indexed="64"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color indexed="64"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color indexed="64"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+  <x:cellXfs count="7">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1349,6 +1522,19 @@
       <mc:Fallback>
         <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="top"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="top"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -2035,2343 +2221,2755 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1" filterMode="1"/>
-  <x:dimension ref="A1:E137"/>
+  <x:dimension ref="A1:F137"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="32" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="31" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="29" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="58" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="28.25" style="4" customWidth="1"/>
+    <x:col min="4" max="4" width="41.75" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="4" customWidth="1"/>
+    <x:col min="6" max="6" width="47.625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="24" customHeight="1">
+    <x:row r="1" spans="1:6" ht="24" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>262</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>250</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
       <x:c r="A2" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E2" s="5">
         <x:v>45296</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
+      <x:c r="F2" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
       <x:c r="A3" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>251</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>168</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E3" s="5">
         <x:v>45303</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
+      <x:c r="F3" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:6">
       <x:c r="A4" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>45310</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
+      <x:c r="F4" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6">
       <x:c r="A5" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>249</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>356</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E5" s="5">
         <x:v>45317</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
+      <x:c r="F5" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6">
       <x:c r="A6" s="3" t="s">
-        <x:v>260</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>264</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>210</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E6" s="5">
         <x:v>45324</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5">
+      <x:c r="F6" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6">
       <x:c r="A7" s="3" t="s">
-        <x:v>271</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E7" s="5">
         <x:v>45331</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
+      <x:c r="F7" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6">
       <x:c r="A8" s="3" t="s">
-        <x:v>254</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E8" s="5">
         <x:v>45338</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5">
+      <x:c r="F8" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6">
       <x:c r="A9" s="3" t="s">
-        <x:v>211</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E9" s="5">
         <x:v>45345</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
+      <x:c r="F9" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6">
       <x:c r="A10" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>265</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>363</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E10" s="5">
         <x:v>45352</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:5">
+      <x:c r="F10" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6">
       <x:c r="A11" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E11" s="5">
         <x:v>45359</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5">
+      <x:c r="F11" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:6">
       <x:c r="A12" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>358</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="E12" s="5">
         <x:v>45366</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5">
+      <x:c r="F12" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:6">
       <x:c r="A13" s="3" t="s">
-        <x:v>271</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>364</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E13" s="5">
         <x:v>45373</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5">
+      <x:c r="F13" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:6">
       <x:c r="A14" s="3" t="s">
-        <x:v>261</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>258</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E14" s="5">
         <x:v>45380</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:5" ht="32.75">
+      <x:c r="F14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6" ht="32.75">
       <x:c r="A15" s="3" t="s">
-        <x:v>354</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>369</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>367</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E15" s="5">
         <x:v>45387</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:5" ht="32.75">
+      <x:c r="F15" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="32.75">
       <x:c r="A16" s="3" t="s">
-        <x:v>248</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>368</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>355</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="E16" s="5">
         <x:v>45394</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5">
+      <x:c r="F16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6">
       <x:c r="A17" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>176</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E17" s="5">
         <x:v>45401</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5">
+      <x:c r="F17" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6">
       <x:c r="A18" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E18" s="5">
         <x:v>45408</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5">
+      <x:c r="F18" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6">
       <x:c r="A19" s="3" t="s">
-        <x:v>267</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E19" s="5">
         <x:v>45415</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" spans="1:5">
+      <x:c r="F19" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6">
       <x:c r="A20" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>357</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E20" s="5">
         <x:v>45422</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" spans="1:5">
+      <x:c r="F20" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6">
       <x:c r="A21" s="3" t="s">
-        <x:v>266</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E21" s="5">
         <x:v>45429</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" spans="1:5">
+      <x:c r="F21" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6">
       <x:c r="A22" s="3" t="s">
-        <x:v>302</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>265</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E22" s="5">
         <x:v>45436</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:5">
+      <x:c r="F22" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:6">
       <x:c r="A23" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>165</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E23" s="5">
         <x:v>45443</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" spans="1:5">
+      <x:c r="F23" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6">
       <x:c r="A24" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E24" s="5">
         <x:v>45450</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" spans="1:5">
+      <x:c r="F24" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6">
       <x:c r="A25" s="3" t="s">
-        <x:v>292</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>276</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>230</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E25" s="5">
         <x:v>45457</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" spans="1:5">
+      <x:c r="F25" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:6">
       <x:c r="A26" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>360</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E26" s="5">
         <x:v>45464</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:5">
+      <x:c r="F26" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:6">
       <x:c r="A27" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E27" s="5">
         <x:v>45471</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:5">
+      <x:c r="F27" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:6">
       <x:c r="A28" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
-        <x:v>275</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E28" s="5">
         <x:v>45478</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:5">
+      <x:c r="F28" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:6">
       <x:c r="A29" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>221</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E29" s="5">
         <x:v>45485</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" spans="1:5">
+      <x:c r="F29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6">
       <x:c r="A30" s="3" t="s">
-        <x:v>294</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E30" s="5">
         <x:v>45492</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" spans="1:5">
+      <x:c r="F30" t="s">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:6">
       <x:c r="A31" s="3" t="s">
-        <x:v>298</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>276</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>359</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E31" s="5">
         <x:v>45499</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" spans="1:5">
+      <x:c r="F31" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:6">
       <x:c r="A32" s="3" t="s">
-        <x:v>272</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E32" s="5">
         <x:v>45506</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" spans="1:5">
+      <x:c r="F32" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:6">
       <x:c r="A33" s="3" t="s">
-        <x:v>279</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
-        <x:v>276</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>156</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E33" s="5">
         <x:v>45513</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" spans="1:5">
+      <x:c r="F33" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:6">
       <x:c r="A34" s="3" t="s">
-        <x:v>281</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>286</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E34" s="5">
         <x:v>45520</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" spans="1:5">
+      <x:c r="F34" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:6">
       <x:c r="A35" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>222</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>172</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E35" s="5">
         <x:v>45534</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" spans="1:5">
+      <x:c r="F35" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:6">
       <x:c r="A36" s="3" t="s">
-        <x:v>288</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E36" s="5">
         <x:v>45541</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" spans="1:5">
+      <x:c r="F36" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:6">
       <x:c r="A37" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>231</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E37" s="5">
         <x:v>45548</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" spans="1:5">
+      <x:c r="F37" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:6">
       <x:c r="A38" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>274</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E38" s="5">
         <x:v>45555</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" spans="1:5">
+      <x:c r="F38" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:6">
       <x:c r="A39" s="3" t="s">
-        <x:v>290</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
-        <x:v>291</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>173</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E39" s="5">
         <x:v>45562</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" spans="1:5">
+      <x:c r="F39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:6">
       <x:c r="A40" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B40" s="3" t="s">
-        <x:v>295</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C40" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D40" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E40" s="5">
         <x:v>45569</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" spans="1:5">
+      <x:c r="F40" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:6">
       <x:c r="A41" s="3" t="s">
-        <x:v>260</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B41" s="3" t="s">
-        <x:v>264</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C41" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D41" s="3" t="s">
-        <x:v>370</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="E41" s="5">
         <x:v>45576</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" spans="1:5">
+      <x:c r="F41" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:6" ht="32.75">
       <x:c r="A42" s="3" t="s">
-        <x:v>293</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B42" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C42" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D42" s="3" t="s">
-        <x:v>226</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E42" s="5">
         <x:v>45583</x:v>
       </x:c>
-    </x:row>
-    <x:row r="43" spans="1:5">
+      <x:c r="F42" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:6">
       <x:c r="A43" s="3" t="s">
-        <x:v>288</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B43" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C43" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D43" s="3" t="s">
-        <x:v>365</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E43" s="5">
         <x:v>45590</x:v>
       </x:c>
-    </x:row>
-    <x:row r="44" spans="1:5">
+      <x:c r="F43" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:6">
       <x:c r="A44" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B44" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C44" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
-        <x:v>361</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E44" s="5">
         <x:v>45597</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45" spans="1:5">
+      <x:c r="F44" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:6" ht="32.75">
       <x:c r="A45" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B45" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C45" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D45" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E45" s="5">
         <x:v>45604</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" spans="1:5">
+      <x:c r="F45" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:6">
       <x:c r="A46" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B46" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C46" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D46" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E46" s="5">
         <x:v>45611</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" spans="1:5">
+      <x:c r="F46" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:6">
       <x:c r="A47" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B47" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C47" s="3" t="s">
-        <x:v>223</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D47" s="3" t="s">
-        <x:v>232</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="E47" s="5">
         <x:v>45618</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" spans="1:5">
+      <x:c r="F47" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:6">
       <x:c r="A48" s="3" t="s">
-        <x:v>273</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B48" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C48" s="3" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C48" s="3" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E48" s="5">
         <x:v>45625</x:v>
       </x:c>
-    </x:row>
-    <x:row r="49" spans="1:5">
+      <x:c r="F48" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:6">
       <x:c r="A49" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B49" s="3" t="s">
-        <x:v>285</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C49" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>371</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E49" s="5">
         <x:v>45632</x:v>
       </x:c>
-    </x:row>
-    <x:row r="50" spans="1:5">
+      <x:c r="F49" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:6">
       <x:c r="A50" s="3" t="s">
-        <x:v>280</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B50" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E50" s="5">
         <x:v>45639</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51" spans="1:5">
+      <x:c r="F50" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:6">
       <x:c r="A51" s="3" t="s">
-        <x:v>283</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B51" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D51" s="3" t="s">
-        <x:v>373</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="E51" s="5">
         <x:v>45646</x:v>
       </x:c>
-    </x:row>
-    <x:row r="52" spans="1:5">
+      <x:c r="F51" t="s">
+        <x:v>420</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:6">
       <x:c r="A52" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B52" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D52" s="3" t="s">
-        <x:v>235</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E52" s="5">
         <x:v>45653</x:v>
       </x:c>
-    </x:row>
-    <x:row r="53" spans="1:5" ht="32.75">
+      <x:c r="F52" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:6" ht="32.75">
       <x:c r="A53" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B53" s="3" t="s">
-        <x:v>377</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D53" s="3" t="s">
-        <x:v>233</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="E53" s="5">
         <x:v>45660</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54" spans="1:5">
+      <x:c r="F53" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:6">
       <x:c r="A54" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B54" s="3" t="s">
-        <x:v>284</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C54" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D54" s="3" t="s">
-        <x:v>234</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="E54" s="5">
         <x:v>45667</x:v>
       </x:c>
-    </x:row>
-    <x:row r="55" spans="1:5">
+      <x:c r="F54" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:6">
       <x:c r="A55" s="3" t="s">
-        <x:v>287</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B55" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C55" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D55" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E55" s="5">
         <x:v>45674</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56" spans="1:5">
+      <x:c r="F55" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:6">
       <x:c r="A56" s="3" t="s">
-        <x:v>281</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B56" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C56" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D56" s="3" t="s">
-        <x:v>159</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E56" s="5">
         <x:v>45681</x:v>
       </x:c>
-    </x:row>
-    <x:row r="57" spans="1:5">
+      <x:c r="F56" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:6">
       <x:c r="A57" s="3" t="s">
-        <x:v>296</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B57" s="3" t="s">
-        <x:v>289</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C57" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D57" s="3" t="s">
-        <x:v>366</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="E57" s="5">
         <x:v>45688</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58" spans="1:5">
+      <x:c r="F57" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:6">
       <x:c r="A58" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B58" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C58" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D58" s="3" t="s">
-        <x:v>372</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="E58" s="5">
         <x:v>45695</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59" spans="1:5">
+      <x:c r="F58" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:6">
       <x:c r="A59" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B59" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C59" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D59" s="3" t="s">
-        <x:v>180</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E59" s="5">
         <x:v>45702</x:v>
       </x:c>
-    </x:row>
-    <x:row r="60" spans="1:5">
+      <x:c r="F59" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:6">
       <x:c r="A60" s="3" t="s">
-        <x:v>288</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B60" s="3" t="s">
-        <x:v>297</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C60" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D60" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E60" s="5">
         <x:v>45709</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61" spans="1:5">
+      <x:c r="F60" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:6">
       <x:c r="A61" s="3" t="s">
-        <x:v>281</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B61" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D61" s="3" t="s">
-        <x:v>362</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="E61" s="5">
         <x:v>45716</x:v>
       </x:c>
-    </x:row>
-    <x:row r="62" spans="1:5">
+      <x:c r="F61" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:6">
       <x:c r="A62" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B62" s="3" t="s">
-        <x:v>301</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C62" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D62" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E62" s="5">
         <x:v>45723</x:v>
       </x:c>
-    </x:row>
-    <x:row r="63" spans="1:5">
+      <x:c r="F62" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:6">
       <x:c r="A63" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B63" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C63" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D63" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E63" s="5">
         <x:v>45730</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64" spans="1:5">
+      <x:c r="F63" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:6">
       <x:c r="A64" s="3" t="s">
-        <x:v>300</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B64" s="3" t="s">
-        <x:v>299</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C64" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D64" s="3" t="s">
-        <x:v>237</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E64" s="5">
         <x:v>45737</x:v>
       </x:c>
-    </x:row>
-    <x:row r="65" spans="1:5">
+      <x:c r="F64" t="s">
+        <x:v>430</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:6">
       <x:c r="A65" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B65" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D65" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E65" s="5">
         <x:v>45744</x:v>
       </x:c>
-    </x:row>
-    <x:row r="66" spans="1:5">
+      <x:c r="F65" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:6">
       <x:c r="A66" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B66" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D66" s="3" t="s">
-        <x:v>181</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E66" s="5">
         <x:v>45751</x:v>
       </x:c>
-    </x:row>
-    <x:row r="67" spans="1:5">
+      <x:c r="F66" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:6">
       <x:c r="A67" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B67" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D67" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E67" s="5">
         <x:v>45758</x:v>
       </x:c>
-    </x:row>
-    <x:row r="68" spans="1:5">
+      <x:c r="F67" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:6">
       <x:c r="A68" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B68" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D68" s="3" t="s">
-        <x:v>374</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E68" s="5">
         <x:v>45765</x:v>
       </x:c>
-    </x:row>
-    <x:row r="69" spans="1:5">
+      <x:c r="F68" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:6">
       <x:c r="A69" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B69" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C69" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D69" s="3" t="s">
-        <x:v>190</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E69" s="5">
         <x:v>45772</x:v>
       </x:c>
-    </x:row>
-    <x:row r="70" spans="1:5">
+      <x:c r="F69" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:6">
       <x:c r="A70" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B70" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C70" s="3" t="s">
-        <x:v>102</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D70" s="3" t="s">
-        <x:v>375</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="E70" s="5">
         <x:v>45779</x:v>
       </x:c>
-    </x:row>
-    <x:row r="71" spans="1:5">
+      <x:c r="F70" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:6">
       <x:c r="A71" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B71" s="3" t="s">
-        <x:v>297</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C71" s="3" t="s">
-        <x:v>323</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D71" s="3" t="s">
-        <x:v>376</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E71" s="5">
         <x:v>45786</x:v>
       </x:c>
-    </x:row>
-    <x:row r="72" spans="1:5">
+      <x:c r="F71" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:6">
       <x:c r="A72" s="3" t="s">
-        <x:v>302</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B72" s="3" t="s">
-        <x:v>311</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C72" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D72" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E72" s="5">
         <x:v>45793</x:v>
       </x:c>
-    </x:row>
-    <x:row r="73" spans="1:5">
+      <x:c r="F72" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:6">
       <x:c r="A73" s="3" t="s">
-        <x:v>314</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B73" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C73" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D73" s="3" t="s">
-        <x:v>392</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E73" s="5">
         <x:v>45800</x:v>
       </x:c>
-    </x:row>
-    <x:row r="74" spans="1:5">
+      <x:c r="F73" t="s">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:6">
       <x:c r="A74" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B74" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D74" s="3" t="s">
-        <x:v>185</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E74" s="5">
         <x:v>45807</x:v>
       </x:c>
-    </x:row>
-    <x:row r="75" spans="1:5">
+      <x:c r="F74" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:6">
       <x:c r="A75" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B75" s="3" t="s">
-        <x:v>289</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C75" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D75" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E75" s="5">
         <x:v>45814</x:v>
       </x:c>
-    </x:row>
-    <x:row r="76" spans="1:5">
+      <x:c r="F75" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:6">
       <x:c r="A76" s="3" t="s">
-        <x:v>326</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B76" s="3" t="s">
-        <x:v>312</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C76" s="3" t="s">
-        <x:v>325</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D76" s="3" t="s">
-        <x:v>324</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E76" s="5">
         <x:v>45821</x:v>
       </x:c>
-    </x:row>
-    <x:row r="77" spans="1:5">
+      <x:c r="F76" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:6">
       <x:c r="A77" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B77" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C77" s="3" t="s">
-        <x:v>327</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D77" s="3" t="s">
-        <x:v>329</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E77" s="5">
         <x:v>45828</x:v>
       </x:c>
-    </x:row>
-    <x:row r="78" spans="1:5">
+      <x:c r="F77" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:6">
       <x:c r="A78" s="3" t="s">
-        <x:v>308</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B78" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C78" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D78" s="3" t="s">
-        <x:v>328</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E78" s="5">
         <x:v>45835</x:v>
       </x:c>
-    </x:row>
-    <x:row r="79" spans="1:5">
+      <x:c r="F78" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:6">
       <x:c r="A79" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B79" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C79" s="3" t="s">
-        <x:v>330</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D79" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E79" s="5">
         <x:v>45842</x:v>
       </x:c>
-    </x:row>
-    <x:row r="80" spans="1:5">
+      <x:c r="F79" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:6">
       <x:c r="A80" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B80" s="3" t="s">
-        <x:v>265</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C80" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D80" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E80" s="5">
         <x:v>45849</x:v>
       </x:c>
-    </x:row>
-    <x:row r="81" spans="1:5">
+      <x:c r="F80" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:6">
       <x:c r="A81" s="3" t="s">
-        <x:v>306</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B81" s="3" t="s">
-        <x:v>313</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C81" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D81" s="3" t="s">
-        <x:v>384</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E81" s="5">
         <x:v>45856</x:v>
       </x:c>
-    </x:row>
-    <x:row r="82" spans="1:5">
+      <x:c r="F81" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:6">
       <x:c r="A82" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B82" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C82" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D82" s="3" t="s">
-        <x:v>188</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E82" s="5">
         <x:v>45863</x:v>
       </x:c>
-    </x:row>
-    <x:row r="83" spans="1:5">
+      <x:c r="F82" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:6">
       <x:c r="A83" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B83" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C83" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D83" s="3" t="s">
-        <x:v>189</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E83" s="5">
         <x:v>45870</x:v>
       </x:c>
-    </x:row>
-    <x:row r="84" spans="1:5">
+      <x:c r="F83" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:6">
       <x:c r="A84" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B84" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C84" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D84" s="3" t="s">
-        <x:v>383</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="E84" s="5">
         <x:v>45877</x:v>
       </x:c>
-    </x:row>
-    <x:row r="85" spans="1:5">
+      <x:c r="F84" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:6">
       <x:c r="A85" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B85" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C85" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D85" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E85" s="5">
         <x:v>45884</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86" spans="1:5">
+      <x:c r="F85" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:6" ht="32.75">
       <x:c r="A86" s="3" t="s">
-        <x:v>304</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B86" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C86" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D86" s="3" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E86" s="5">
         <x:v>45891</x:v>
       </x:c>
-    </x:row>
-    <x:row r="87" spans="1:5">
+      <x:c r="F86" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:6">
       <x:c r="A87" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B87" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C87" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D87" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E87" s="5">
         <x:v>45905</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88" spans="1:5">
+      <x:c r="F87" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:6">
       <x:c r="A88" s="3" t="s">
-        <x:v>279</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B88" s="3" t="s">
-        <x:v>249</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C88" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D88" s="3" t="s">
-        <x:v>331</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E88" s="5">
         <x:v>45912</x:v>
       </x:c>
-    </x:row>
-    <x:row r="89" spans="1:5">
+      <x:c r="F88" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:6">
       <x:c r="A89" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B89" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C89" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D89" s="3" t="s">
-        <x:v>394</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E89" s="5">
         <x:v>45919</x:v>
       </x:c>
-    </x:row>
-    <x:row r="90" spans="1:5">
+      <x:c r="F89" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:6">
       <x:c r="A90" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B90" s="3" t="s">
-        <x:v>307</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C90" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D90" s="3" t="s">
-        <x:v>378</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E90" s="5">
         <x:v>45926</x:v>
       </x:c>
-    </x:row>
-    <x:row r="91" spans="1:5">
+      <x:c r="F90" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:6">
       <x:c r="A91" s="3" t="s">
-        <x:v>298</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B91" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C91" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D91" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E91" s="5">
         <x:v>45933</x:v>
       </x:c>
-    </x:row>
-    <x:row r="92" spans="1:5">
+      <x:c r="F91" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:6">
       <x:c r="A92" s="3" t="s">
-        <x:v>332</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B92" s="3" t="s">
-        <x:v>336</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C92" s="3" t="s">
-        <x:v>107</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D92" s="3" t="s">
-        <x:v>241</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E92" s="5">
         <x:v>45940</x:v>
       </x:c>
-    </x:row>
-    <x:row r="93" spans="1:5">
+      <x:c r="F92" t="s">
+        <x:v>428</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:6">
       <x:c r="A93" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B93" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C93" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D93" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E93" s="5">
         <x:v>45947</x:v>
       </x:c>
-    </x:row>
-    <x:row r="94" spans="1:5">
+      <x:c r="F93" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:6">
       <x:c r="A94" s="3" t="s">
-        <x:v>333</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B94" s="3" t="s">
-        <x:v>334</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C94" s="3" t="s">
-        <x:v>335</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D94" s="3" t="s">
-        <x:v>385</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E94" s="5">
         <x:v>45954</x:v>
       </x:c>
-    </x:row>
-    <x:row r="95" spans="1:5">
+      <x:c r="F94" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:6">
       <x:c r="A95" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B95" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C95" s="3" t="s">
-        <x:v>337</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D95" s="3" t="s">
-        <x:v>192</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E95" s="5">
         <x:v>45961</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" spans="1:5">
+      <x:c r="F95" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:6">
       <x:c r="A96" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B96" s="3" t="s">
-        <x:v>251</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C96" s="3" t="s">
-        <x:v>116</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D96" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E96" s="5">
         <x:v>45968</x:v>
       </x:c>
-    </x:row>
-    <x:row r="97" spans="1:5">
+      <x:c r="F96" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:6">
       <x:c r="A97" s="3" t="s">
-        <x:v>302</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B97" s="3" t="s">
-        <x:v>291</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C97" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D97" s="3" t="s">
-        <x:v>379</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E97" s="5">
         <x:v>45975</x:v>
       </x:c>
-    </x:row>
-    <x:row r="98" spans="1:5">
+      <x:c r="F97" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:6">
       <x:c r="A98" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B98" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C98" s="3" t="s">
-        <x:v>338</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D98" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E98" s="5">
         <x:v>45982</x:v>
       </x:c>
-    </x:row>
-    <x:row r="99" spans="1:5">
+      <x:c r="F98" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:6">
       <x:c r="A99" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B99" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C99" s="3" t="s">
-        <x:v>309</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="D99" s="3" t="s">
-        <x:v>339</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E99" s="5">
         <x:v>45989</x:v>
       </x:c>
-    </x:row>
-    <x:row r="100" spans="1:5">
+      <x:c r="F99" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:6">
       <x:c r="A100" s="3" t="s">
-        <x:v>288</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B100" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C100" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D100" s="3" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E100" s="5">
         <x:v>45996</x:v>
       </x:c>
-    </x:row>
-    <x:row r="101" spans="1:5">
+      <x:c r="F100" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:6">
       <x:c r="A101" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B101" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C101" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D101" s="3" t="s">
-        <x:v>393</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="E101" s="5">
         <x:v>46003</x:v>
       </x:c>
-    </x:row>
-    <x:row r="102" spans="1:5">
+      <x:c r="F101" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:6">
       <x:c r="A102" s="3" t="s">
-        <x:v>340</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B102" s="3" t="s">
-        <x:v>305</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C102" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D102" s="3" t="s">
-        <x:v>388</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E102" s="5">
         <x:v>46010</x:v>
       </x:c>
-    </x:row>
-    <x:row r="103" spans="1:5">
+      <x:c r="F102" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:6">
       <x:c r="A103" s="3" t="s">
-        <x:v>321</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B103" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C103" s="3" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C103" s="3" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="D103" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E103" s="5">
         <x:v>46017</x:v>
       </x:c>
-    </x:row>
-    <x:row r="104" spans="1:5">
+      <x:c r="F103" t="s">
+        <x:v>441</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:6">
       <x:c r="A104" s="3" t="s">
-        <x:v>271</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B104" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C104" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D104" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E104" s="5">
         <x:v>46024</x:v>
       </x:c>
-    </x:row>
-    <x:row r="105" spans="1:5">
+      <x:c r="F104" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:6">
       <x:c r="A105" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B105" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C105" s="3" t="s">
-        <x:v>309</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="D105" s="3" t="s">
-        <x:v>391</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="E105" s="5">
         <x:v>46031</x:v>
       </x:c>
-    </x:row>
-    <x:row r="106" spans="1:5">
+      <x:c r="F105" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:6">
       <x:c r="A106" s="3" t="s">
-        <x:v>319</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B106" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C106" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D106" s="3" t="s">
-        <x:v>243</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E106" s="5">
         <x:v>46038</x:v>
       </x:c>
-    </x:row>
-    <x:row r="107" spans="1:5">
+      <x:c r="F106" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:6">
       <x:c r="A107" s="3" t="s">
-        <x:v>314</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B107" s="3" t="s">
-        <x:v>341</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C107" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D107" s="3" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E107" s="5">
         <x:v>46045</x:v>
       </x:c>
-    </x:row>
-    <x:row r="108" spans="1:5">
+      <x:c r="F107" t="s">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:6">
       <x:c r="A108" s="3" t="s">
-        <x:v>281</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B108" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C108" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D108" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E108" s="5">
         <x:v>46052</x:v>
       </x:c>
-    </x:row>
-    <x:row r="109" spans="1:5">
+      <x:c r="F108" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:6">
       <x:c r="A109" s="3" t="s">
-        <x:v>317</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B109" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C109" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D109" s="3" t="s">
-        <x:v>200</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E109" s="5">
         <x:v>46059</x:v>
       </x:c>
-    </x:row>
-    <x:row r="110" spans="1:5">
+      <x:c r="F109" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:6" ht="32.75">
       <x:c r="A110" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B110" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C110" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D110" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E110" s="5">
         <x:v>46066</x:v>
       </x:c>
-    </x:row>
-    <x:row r="111" spans="1:5">
+      <x:c r="F110" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:6">
       <x:c r="A111" s="3" t="s">
-        <x:v>322</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B111" s="3" t="s">
-        <x:v>291</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C111" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D111" s="3" t="s">
-        <x:v>244</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E111" s="5">
         <x:v>46073</x:v>
       </x:c>
-    </x:row>
-    <x:row r="112" spans="1:5">
+      <x:c r="F111" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:6">
       <x:c r="A112" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B112" s="3" t="s">
-        <x:v>318</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C112" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D112" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E112" s="5">
         <x:v>46080</x:v>
       </x:c>
-    </x:row>
-    <x:row r="113" spans="1:5">
+      <x:c r="F112" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:6">
       <x:c r="A113" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B113" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C113" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D113" s="3" t="s">
-        <x:v>245</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E113" s="5">
         <x:v>46087</x:v>
       </x:c>
-    </x:row>
-    <x:row r="114" spans="1:5">
+      <x:c r="F113" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:6">
       <x:c r="A114" s="3" t="s">
-        <x:v>342</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B114" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C114" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D114" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E114" s="5">
         <x:v>46094</x:v>
       </x:c>
-    </x:row>
-    <x:row r="115" spans="1:5">
+      <x:c r="F114" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:6">
       <x:c r="A115" s="3" t="s">
-        <x:v>271</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B115" s="3" t="s">
-        <x:v>303</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C115" s="3" t="s">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D115" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E115" s="5">
         <x:v>46101</x:v>
       </x:c>
-    </x:row>
-    <x:row r="116" spans="1:5">
+      <x:c r="F115" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:6">
       <x:c r="A116" s="3" t="s">
-        <x:v>320</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B116" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C116" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D116" s="3" t="s">
-        <x:v>246</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E116" s="5">
         <x:v>46108</x:v>
       </x:c>
-    </x:row>
-    <x:row r="117" spans="1:5">
+      <x:c r="F116" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:6">
       <x:c r="A117" s="3" t="s">
-        <x:v>292</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B117" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C117" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D117" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E117" s="5">
         <x:v>46115</x:v>
       </x:c>
-    </x:row>
-    <x:row r="118" spans="1:5">
+      <x:c r="F117" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:6">
       <x:c r="A118" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B118" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C118" s="3" t="s">
-        <x:v>343</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D118" s="3" t="s">
-        <x:v>196</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E118" s="5">
         <x:v>46122</x:v>
       </x:c>
-    </x:row>
-    <x:row r="119" spans="1:5">
+      <x:c r="F118" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:6">
       <x:c r="A119" s="3" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B119" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C119" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D119" s="3" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="B119" s="3" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C119" s="3" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D119" s="3" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="E119" s="5">
         <x:v>46129</x:v>
       </x:c>
-    </x:row>
-    <x:row r="120" spans="1:5">
+      <x:c r="F119" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:6">
       <x:c r="A120" s="3" t="s">
-        <x:v>254</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B120" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C120" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D120" s="3" t="s">
-        <x:v>380</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E120" s="5">
         <x:v>46136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="121" spans="1:5">
+      <x:c r="F120" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:6" ht="32.75">
       <x:c r="A121" s="3" t="s">
-        <x:v>298</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B121" s="3" t="s">
-        <x:v>313</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C121" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D121" s="3" t="s">
-        <x:v>151</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E121" s="5">
         <x:v>46143</x:v>
       </x:c>
-    </x:row>
-    <x:row r="122" spans="1:5">
+      <x:c r="F121" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:6">
       <x:c r="A122" s="3" t="s">
-        <x:v>273</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B122" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C122" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D122" s="3" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E122" s="5">
         <x:v>46150</x:v>
       </x:c>
-    </x:row>
-    <x:row r="123" spans="1:5">
+      <x:c r="F122" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:6">
       <x:c r="A123" s="3" t="s">
-        <x:v>344</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B123" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C123" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D123" s="3" t="s">
-        <x:v>386</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="E123" s="5">
         <x:v>46157</x:v>
       </x:c>
-    </x:row>
-    <x:row r="124" spans="1:5">
+      <x:c r="F123" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:6">
       <x:c r="A124" s="3" t="s">
-        <x:v>287</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B124" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C124" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D124" s="3" t="s">
-        <x:v>390</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E124" s="5">
         <x:v>46164</x:v>
       </x:c>
-    </x:row>
-    <x:row r="125" spans="1:5">
+      <x:c r="F124" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:6">
       <x:c r="A125" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B125" s="3" t="s">
-        <x:v>197</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C125" s="3" t="s">
-        <x:v>345</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D125" s="3" t="s">
-        <x:v>381</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E125" s="5">
         <x:v>46171</x:v>
       </x:c>
-    </x:row>
-    <x:row r="126" spans="1:5">
+      <x:c r="F125" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:6">
       <x:c r="A126" s="3" t="s">
-        <x:v>346</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B126" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C126" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D126" s="3" t="s">
-        <x:v>229</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E126" s="5">
         <x:v>46178</x:v>
       </x:c>
-    </x:row>
-    <x:row r="127" spans="1:5">
+      <x:c r="F126" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:6">
       <x:c r="A127" s="3" t="s">
-        <x:v>263</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B127" s="3" t="s">
-        <x:v>195</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C127" s="3" t="s">
-        <x:v>143</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D127" s="3" t="s">
-        <x:v>382</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="E127" s="5">
         <x:v>46185</x:v>
       </x:c>
-    </x:row>
-    <x:row r="128" spans="1:5">
+      <x:c r="F127" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:6">
       <x:c r="A128" s="3" t="s">
-        <x:v>347</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B128" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C128" s="3" t="s">
-        <x:v>349</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D128" s="3" t="s">
-        <x:v>389</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E128" s="5">
         <x:v>46192</x:v>
       </x:c>
-    </x:row>
-    <x:row r="129" spans="1:5">
+      <x:c r="F128" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:6">
       <x:c r="A129" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B129" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C129" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D129" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E129" s="5">
         <x:v>46199</x:v>
       </x:c>
-    </x:row>
-    <x:row r="130" spans="1:5">
+      <x:c r="F129" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:6">
       <x:c r="A130" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B130" s="3" t="s">
-        <x:v>289</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C130" s="3" t="s">
-        <x:v>348</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D130" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E130" s="5">
         <x:v>46206</x:v>
       </x:c>
-    </x:row>
-    <x:row r="131" spans="1:5">
+      <x:c r="F130" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:6">
       <x:c r="A131" s="3" t="s">
-        <x:v>346</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B131" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C131" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D131" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E131" s="5">
         <x:v>46213</x:v>
       </x:c>
-    </x:row>
-    <x:row r="132" spans="1:5">
+      <x:c r="F131" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:6">
       <x:c r="A132" s="3" t="s">
-        <x:v>351</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B132" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C132" s="3" t="s">
-        <x:v>350</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D132" s="3" t="s">
-        <x:v>194</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E132" s="5">
         <x:v>46220</x:v>
       </x:c>
-    </x:row>
-    <x:row r="133" spans="1:5">
+      <x:c r="F132" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:6">
       <x:c r="A133" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B133" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C133" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D133" s="3" t="s">
-        <x:v>315</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="E133" s="5">
         <x:v>46227</x:v>
       </x:c>
-    </x:row>
-    <x:row r="134" spans="1:5">
+      <x:c r="F133" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:6">
       <x:c r="A134" s="3" t="s">
-        <x:v>304</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B134" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C134" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D134" s="3" t="s">
-        <x:v>310</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E134" s="5">
         <x:v>46234</x:v>
       </x:c>
-    </x:row>
-    <x:row r="135" spans="1:5">
+      <x:c r="F134" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:6">
       <x:c r="A135" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B135" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C135" s="3" t="s">
-        <x:v>352</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D135" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E135" s="5">
         <x:v>46241</x:v>
       </x:c>
-    </x:row>
-    <x:row r="136" spans="1:5">
+      <x:c r="F135" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:6">
       <x:c r="A136" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B136" s="3" t="s">
-        <x:v>313</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C136" s="3" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D136" s="3" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="D136" s="3" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E136" s="5">
         <x:v>46248</x:v>
       </x:c>
-    </x:row>
-    <x:row r="137" spans="1:5">
+      <x:c r="F136" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:6">
       <x:c r="A137" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B137" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C137" s="3" t="s">
-        <x:v>353</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D137" s="3" t="s">
-        <x:v>316</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E137" s="5">
         <x:v>46255</x:v>
+      </x:c>
+      <x:c r="F137" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
